--- a/data/seed-density.xlsx
+++ b/data/seed-density.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lopazanski/Documents/github/seed-density-clams/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30543D2D-2862-9045-B3FA-A7C8667E9C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942913C5-EB1D-C246-BC6D-45CB4F8ADE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{6DF92C54-7A3D-F34F-8EE7-229927638087}"/>
+    <workbookView xWindow="4600" yWindow="600" windowWidth="37380" windowHeight="26320" xr2:uid="{6DF92C54-7A3D-F34F-8EE7-229927638087}"/>
   </bookViews>
   <sheets>
     <sheet name="seed-density" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5048" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5688" uniqueCount="47">
   <si>
     <t>plot_id</t>
   </si>
@@ -185,7 +185,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -247,10 +247,11 @@
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -585,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A3A4A9A-9719-DB49-ADBE-C2C85B5F3579}">
-  <dimension ref="A1:Q681"/>
+  <dimension ref="A1:T761"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="11" max="15" width="12.5" style="8" customWidth="1"/>
@@ -35353,7 +35354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A673" s="1">
         <v>46113</v>
       </c>
@@ -35403,7 +35404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A674" s="1">
         <v>46113</v>
       </c>
@@ -35453,7 +35454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="675" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A675" s="1">
         <v>46113</v>
       </c>
@@ -35503,7 +35504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="676" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A676" s="1">
         <v>46113</v>
       </c>
@@ -35553,7 +35554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="677" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A677" s="1">
         <v>46113</v>
       </c>
@@ -35603,7 +35604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="678" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A678" s="1">
         <v>46113</v>
       </c>
@@ -35653,7 +35654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="679" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A679" s="1">
         <v>46113</v>
       </c>
@@ -35703,7 +35704,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="680" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A680" s="1">
         <v>46113</v>
       </c>
@@ -35753,7 +35754,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="681" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A681" s="1">
         <v>46113</v>
       </c>
@@ -35806,8 +35807,4013 @@
         <v>45</v>
       </c>
     </row>
+    <row r="682" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A682" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B682">
+        <v>1</v>
+      </c>
+      <c r="C682">
+        <v>10</v>
+      </c>
+      <c r="D682">
+        <v>1</v>
+      </c>
+      <c r="E682" t="s">
+        <v>32</v>
+      </c>
+      <c r="F682" t="s">
+        <v>32</v>
+      </c>
+      <c r="G682" t="s">
+        <v>32</v>
+      </c>
+      <c r="H682" t="s">
+        <v>32</v>
+      </c>
+      <c r="I682" t="s">
+        <v>32</v>
+      </c>
+      <c r="J682">
+        <v>0</v>
+      </c>
+      <c r="K682" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L682" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M682" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N682" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O682" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P682" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="683" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A683" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B683">
+        <v>2</v>
+      </c>
+      <c r="C683">
+        <v>10</v>
+      </c>
+      <c r="D683">
+        <v>1</v>
+      </c>
+      <c r="E683" t="s">
+        <v>32</v>
+      </c>
+      <c r="F683" t="s">
+        <v>32</v>
+      </c>
+      <c r="G683" t="s">
+        <v>32</v>
+      </c>
+      <c r="H683" t="s">
+        <v>32</v>
+      </c>
+      <c r="I683" t="s">
+        <v>32</v>
+      </c>
+      <c r="J683">
+        <v>0</v>
+      </c>
+      <c r="K683" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L683" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M683" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N683" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O683" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P683" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="684" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A684" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B684">
+        <v>3</v>
+      </c>
+      <c r="C684">
+        <v>10</v>
+      </c>
+      <c r="D684">
+        <v>1</v>
+      </c>
+      <c r="E684" t="s">
+        <v>32</v>
+      </c>
+      <c r="F684" t="s">
+        <v>32</v>
+      </c>
+      <c r="G684" t="s">
+        <v>32</v>
+      </c>
+      <c r="H684" t="s">
+        <v>32</v>
+      </c>
+      <c r="I684" t="s">
+        <v>32</v>
+      </c>
+      <c r="J684">
+        <v>0</v>
+      </c>
+      <c r="K684" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L684" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M684" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N684" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O684" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P684" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A685" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B685">
+        <v>4</v>
+      </c>
+      <c r="C685">
+        <v>10</v>
+      </c>
+      <c r="D685">
+        <v>1</v>
+      </c>
+      <c r="E685" t="s">
+        <v>32</v>
+      </c>
+      <c r="F685" t="s">
+        <v>32</v>
+      </c>
+      <c r="G685" t="s">
+        <v>32</v>
+      </c>
+      <c r="H685" t="s">
+        <v>32</v>
+      </c>
+      <c r="I685" t="s">
+        <v>32</v>
+      </c>
+      <c r="J685">
+        <v>0</v>
+      </c>
+      <c r="K685" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L685" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M685" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N685" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O685" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P685" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A686" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B686">
+        <v>5</v>
+      </c>
+      <c r="C686">
+        <v>10</v>
+      </c>
+      <c r="D686">
+        <v>0</v>
+      </c>
+      <c r="E686" t="s">
+        <v>32</v>
+      </c>
+      <c r="F686" t="s">
+        <v>32</v>
+      </c>
+      <c r="G686" t="s">
+        <v>32</v>
+      </c>
+      <c r="H686" t="s">
+        <v>32</v>
+      </c>
+      <c r="I686" t="s">
+        <v>32</v>
+      </c>
+      <c r="J686">
+        <v>0</v>
+      </c>
+      <c r="K686" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L686" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M686" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N686" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O686" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P686" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A687" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B687">
+        <v>6</v>
+      </c>
+      <c r="C687">
+        <v>10</v>
+      </c>
+      <c r="D687">
+        <v>0</v>
+      </c>
+      <c r="E687" t="s">
+        <v>32</v>
+      </c>
+      <c r="F687" t="s">
+        <v>32</v>
+      </c>
+      <c r="G687" t="s">
+        <v>32</v>
+      </c>
+      <c r="H687" t="s">
+        <v>32</v>
+      </c>
+      <c r="I687" t="s">
+        <v>32</v>
+      </c>
+      <c r="J687">
+        <v>4</v>
+      </c>
+      <c r="K687" s="8">
+        <v>15</v>
+      </c>
+      <c r="L687" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="M687" s="8">
+        <v>9.1</v>
+      </c>
+      <c r="N687" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="O687" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P687" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q687" s="9"/>
+      <c r="R687" s="9"/>
+      <c r="S687" s="9"/>
+      <c r="T687" s="9"/>
+    </row>
+    <row r="688" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A688" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B688">
+        <v>7</v>
+      </c>
+      <c r="C688">
+        <v>10</v>
+      </c>
+      <c r="D688">
+        <v>0</v>
+      </c>
+      <c r="E688" t="s">
+        <v>32</v>
+      </c>
+      <c r="F688" t="s">
+        <v>32</v>
+      </c>
+      <c r="G688" t="s">
+        <v>32</v>
+      </c>
+      <c r="H688" t="s">
+        <v>32</v>
+      </c>
+      <c r="I688" t="s">
+        <v>32</v>
+      </c>
+      <c r="J688">
+        <v>0</v>
+      </c>
+      <c r="K688" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L688" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M688" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N688" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O688" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P688" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A689" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B689">
+        <v>8</v>
+      </c>
+      <c r="C689">
+        <v>10</v>
+      </c>
+      <c r="D689">
+        <v>0</v>
+      </c>
+      <c r="E689" t="s">
+        <v>32</v>
+      </c>
+      <c r="F689" t="s">
+        <v>32</v>
+      </c>
+      <c r="G689" t="s">
+        <v>32</v>
+      </c>
+      <c r="H689" t="s">
+        <v>32</v>
+      </c>
+      <c r="I689" t="s">
+        <v>32</v>
+      </c>
+      <c r="J689">
+        <v>0</v>
+      </c>
+      <c r="K689" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L689" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M689" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N689" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O689" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P689" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A690" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B690">
+        <v>9</v>
+      </c>
+      <c r="C690">
+        <v>20</v>
+      </c>
+      <c r="D690">
+        <v>1</v>
+      </c>
+      <c r="E690" t="s">
+        <v>32</v>
+      </c>
+      <c r="F690" t="s">
+        <v>32</v>
+      </c>
+      <c r="G690" t="s">
+        <v>32</v>
+      </c>
+      <c r="H690" t="s">
+        <v>32</v>
+      </c>
+      <c r="I690" t="s">
+        <v>32</v>
+      </c>
+      <c r="J690">
+        <v>17</v>
+      </c>
+      <c r="K690" s="8">
+        <v>11.9</v>
+      </c>
+      <c r="L690" s="8">
+        <v>10.8</v>
+      </c>
+      <c r="M690" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="N690" s="8">
+        <v>9.4</v>
+      </c>
+      <c r="O690" s="8">
+        <v>12.5</v>
+      </c>
+      <c r="P690" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="691" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A691" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B691">
+        <v>10</v>
+      </c>
+      <c r="C691">
+        <v>20</v>
+      </c>
+      <c r="D691">
+        <v>1</v>
+      </c>
+      <c r="E691" t="s">
+        <v>32</v>
+      </c>
+      <c r="F691" t="s">
+        <v>32</v>
+      </c>
+      <c r="G691" t="s">
+        <v>32</v>
+      </c>
+      <c r="H691" t="s">
+        <v>32</v>
+      </c>
+      <c r="I691" t="s">
+        <v>32</v>
+      </c>
+      <c r="J691">
+        <v>10</v>
+      </c>
+      <c r="K691" s="8">
+        <v>14.2</v>
+      </c>
+      <c r="L691" s="8">
+        <v>11.5</v>
+      </c>
+      <c r="M691" s="8">
+        <v>10.6</v>
+      </c>
+      <c r="N691" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="O691" s="8">
+        <v>10.7</v>
+      </c>
+      <c r="P691" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="692" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A692" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B692">
+        <v>11</v>
+      </c>
+      <c r="C692">
+        <v>20</v>
+      </c>
+      <c r="D692">
+        <v>1</v>
+      </c>
+      <c r="E692" t="s">
+        <v>32</v>
+      </c>
+      <c r="F692" t="s">
+        <v>32</v>
+      </c>
+      <c r="G692" t="s">
+        <v>32</v>
+      </c>
+      <c r="H692" t="s">
+        <v>32</v>
+      </c>
+      <c r="I692" t="s">
+        <v>32</v>
+      </c>
+      <c r="J692">
+        <v>6</v>
+      </c>
+      <c r="K692" s="8">
+        <v>8.9</v>
+      </c>
+      <c r="L692" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="M692" s="8">
+        <v>6</v>
+      </c>
+      <c r="N692" s="8">
+        <v>9.6</v>
+      </c>
+      <c r="O692" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="P692" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A693" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B693">
+        <v>12</v>
+      </c>
+      <c r="C693">
+        <v>20</v>
+      </c>
+      <c r="D693">
+        <v>1</v>
+      </c>
+      <c r="E693" t="s">
+        <v>32</v>
+      </c>
+      <c r="F693" t="s">
+        <v>32</v>
+      </c>
+      <c r="G693" t="s">
+        <v>32</v>
+      </c>
+      <c r="H693" t="s">
+        <v>32</v>
+      </c>
+      <c r="I693" t="s">
+        <v>32</v>
+      </c>
+      <c r="J693">
+        <v>0</v>
+      </c>
+      <c r="K693" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L693" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M693" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N693" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O693" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P693" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A694" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B694">
+        <v>13</v>
+      </c>
+      <c r="C694">
+        <v>20</v>
+      </c>
+      <c r="D694">
+        <v>0</v>
+      </c>
+      <c r="E694" t="s">
+        <v>32</v>
+      </c>
+      <c r="F694" t="s">
+        <v>32</v>
+      </c>
+      <c r="G694" t="s">
+        <v>32</v>
+      </c>
+      <c r="H694" t="s">
+        <v>32</v>
+      </c>
+      <c r="I694" t="s">
+        <v>32</v>
+      </c>
+      <c r="J694">
+        <v>0</v>
+      </c>
+      <c r="K694" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L694" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M694" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N694" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O694" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P694" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A695" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B695">
+        <v>14</v>
+      </c>
+      <c r="C695">
+        <v>20</v>
+      </c>
+      <c r="D695">
+        <v>0</v>
+      </c>
+      <c r="E695" t="s">
+        <v>32</v>
+      </c>
+      <c r="F695" t="s">
+        <v>32</v>
+      </c>
+      <c r="G695" t="s">
+        <v>32</v>
+      </c>
+      <c r="H695" t="s">
+        <v>32</v>
+      </c>
+      <c r="I695" t="s">
+        <v>32</v>
+      </c>
+      <c r="J695">
+        <v>0</v>
+      </c>
+      <c r="K695" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L695" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M695" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N695" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O695" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P695" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A696" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B696">
+        <v>15</v>
+      </c>
+      <c r="C696">
+        <v>20</v>
+      </c>
+      <c r="D696">
+        <v>0</v>
+      </c>
+      <c r="E696" t="s">
+        <v>32</v>
+      </c>
+      <c r="F696" t="s">
+        <v>32</v>
+      </c>
+      <c r="G696" t="s">
+        <v>32</v>
+      </c>
+      <c r="H696" t="s">
+        <v>32</v>
+      </c>
+      <c r="I696" t="s">
+        <v>32</v>
+      </c>
+      <c r="J696">
+        <v>0</v>
+      </c>
+      <c r="K696" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L696" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M696" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N696" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O696" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P696" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A697" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B697">
+        <v>16</v>
+      </c>
+      <c r="C697">
+        <v>20</v>
+      </c>
+      <c r="D697">
+        <v>0</v>
+      </c>
+      <c r="E697" t="s">
+        <v>32</v>
+      </c>
+      <c r="F697" t="s">
+        <v>32</v>
+      </c>
+      <c r="G697" t="s">
+        <v>32</v>
+      </c>
+      <c r="H697" t="s">
+        <v>32</v>
+      </c>
+      <c r="I697" t="s">
+        <v>32</v>
+      </c>
+      <c r="J697">
+        <v>1</v>
+      </c>
+      <c r="K697" s="8">
+        <v>5.5</v>
+      </c>
+      <c r="L697" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M697" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N697" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O697" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P697" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A698" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B698">
+        <v>17</v>
+      </c>
+      <c r="C698">
+        <v>30</v>
+      </c>
+      <c r="D698">
+        <v>1</v>
+      </c>
+      <c r="E698" t="s">
+        <v>32</v>
+      </c>
+      <c r="F698" t="s">
+        <v>32</v>
+      </c>
+      <c r="G698" t="s">
+        <v>32</v>
+      </c>
+      <c r="H698" t="s">
+        <v>32</v>
+      </c>
+      <c r="I698" t="s">
+        <v>32</v>
+      </c>
+      <c r="J698">
+        <v>0</v>
+      </c>
+      <c r="K698" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L698" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M698" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N698" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O698" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P698" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A699" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B699">
+        <v>18</v>
+      </c>
+      <c r="C699">
+        <v>30</v>
+      </c>
+      <c r="D699">
+        <v>1</v>
+      </c>
+      <c r="E699" t="s">
+        <v>32</v>
+      </c>
+      <c r="F699" t="s">
+        <v>32</v>
+      </c>
+      <c r="G699" t="s">
+        <v>32</v>
+      </c>
+      <c r="H699" t="s">
+        <v>32</v>
+      </c>
+      <c r="I699" t="s">
+        <v>32</v>
+      </c>
+      <c r="J699">
+        <v>0</v>
+      </c>
+      <c r="K699" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L699" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M699" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N699" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O699" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P699" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A700" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B700">
+        <v>19</v>
+      </c>
+      <c r="C700">
+        <v>30</v>
+      </c>
+      <c r="D700">
+        <v>1</v>
+      </c>
+      <c r="E700" t="s">
+        <v>32</v>
+      </c>
+      <c r="F700" t="s">
+        <v>32</v>
+      </c>
+      <c r="G700" t="s">
+        <v>32</v>
+      </c>
+      <c r="H700" t="s">
+        <v>32</v>
+      </c>
+      <c r="I700" t="s">
+        <v>32</v>
+      </c>
+      <c r="J700">
+        <v>0</v>
+      </c>
+      <c r="K700" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L700" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M700" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N700" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O700" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P700" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A701" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B701">
+        <v>20</v>
+      </c>
+      <c r="C701">
+        <v>30</v>
+      </c>
+      <c r="D701">
+        <v>1</v>
+      </c>
+      <c r="E701" t="s">
+        <v>32</v>
+      </c>
+      <c r="F701" t="s">
+        <v>32</v>
+      </c>
+      <c r="G701" t="s">
+        <v>32</v>
+      </c>
+      <c r="H701" t="s">
+        <v>32</v>
+      </c>
+      <c r="I701" t="s">
+        <v>32</v>
+      </c>
+      <c r="J701">
+        <v>0</v>
+      </c>
+      <c r="K701" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L701" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M701" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N701" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O701" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P701" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A702" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B702">
+        <v>21</v>
+      </c>
+      <c r="C702">
+        <v>30</v>
+      </c>
+      <c r="D702">
+        <v>0</v>
+      </c>
+      <c r="E702" t="s">
+        <v>32</v>
+      </c>
+      <c r="F702" t="s">
+        <v>32</v>
+      </c>
+      <c r="G702" t="s">
+        <v>32</v>
+      </c>
+      <c r="H702" t="s">
+        <v>32</v>
+      </c>
+      <c r="I702" t="s">
+        <v>32</v>
+      </c>
+      <c r="J702">
+        <v>0</v>
+      </c>
+      <c r="K702" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L702" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M702" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N702" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O702" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P702" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A703" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B703">
+        <v>22</v>
+      </c>
+      <c r="C703">
+        <v>30</v>
+      </c>
+      <c r="D703">
+        <v>0</v>
+      </c>
+      <c r="E703" t="s">
+        <v>32</v>
+      </c>
+      <c r="F703" t="s">
+        <v>32</v>
+      </c>
+      <c r="G703" t="s">
+        <v>32</v>
+      </c>
+      <c r="H703" t="s">
+        <v>32</v>
+      </c>
+      <c r="I703" t="s">
+        <v>32</v>
+      </c>
+      <c r="J703">
+        <v>6</v>
+      </c>
+      <c r="K703" s="8">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L703" s="8">
+        <v>15.5</v>
+      </c>
+      <c r="M703" s="8">
+        <v>19.8</v>
+      </c>
+      <c r="N703" s="8">
+        <v>15</v>
+      </c>
+      <c r="O703" s="8">
+        <v>16</v>
+      </c>
+      <c r="P703" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="704" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A704" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B704">
+        <v>23</v>
+      </c>
+      <c r="C704">
+        <v>30</v>
+      </c>
+      <c r="D704">
+        <v>0</v>
+      </c>
+      <c r="E704" t="s">
+        <v>32</v>
+      </c>
+      <c r="F704" t="s">
+        <v>32</v>
+      </c>
+      <c r="G704" t="s">
+        <v>32</v>
+      </c>
+      <c r="H704" t="s">
+        <v>32</v>
+      </c>
+      <c r="I704" t="s">
+        <v>32</v>
+      </c>
+      <c r="J704">
+        <v>0</v>
+      </c>
+      <c r="K704" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L704" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M704" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N704" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O704" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P704" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A705" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B705">
+        <v>24</v>
+      </c>
+      <c r="C705">
+        <v>30</v>
+      </c>
+      <c r="D705">
+        <v>0</v>
+      </c>
+      <c r="E705" t="s">
+        <v>32</v>
+      </c>
+      <c r="F705" t="s">
+        <v>32</v>
+      </c>
+      <c r="G705" t="s">
+        <v>32</v>
+      </c>
+      <c r="H705" t="s">
+        <v>32</v>
+      </c>
+      <c r="I705" t="s">
+        <v>32</v>
+      </c>
+      <c r="J705">
+        <v>0</v>
+      </c>
+      <c r="K705" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L705" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M705" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N705" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O705" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P705" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A706" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B706">
+        <v>25</v>
+      </c>
+      <c r="C706">
+        <v>40</v>
+      </c>
+      <c r="D706">
+        <v>1</v>
+      </c>
+      <c r="E706" t="s">
+        <v>32</v>
+      </c>
+      <c r="F706" t="s">
+        <v>32</v>
+      </c>
+      <c r="G706" t="s">
+        <v>32</v>
+      </c>
+      <c r="H706" t="s">
+        <v>32</v>
+      </c>
+      <c r="I706" t="s">
+        <v>32</v>
+      </c>
+      <c r="J706">
+        <v>0</v>
+      </c>
+      <c r="K706" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L706" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M706" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N706" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O706" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P706" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A707" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B707">
+        <v>26</v>
+      </c>
+      <c r="C707">
+        <v>40</v>
+      </c>
+      <c r="D707">
+        <v>1</v>
+      </c>
+      <c r="E707" t="s">
+        <v>32</v>
+      </c>
+      <c r="F707" t="s">
+        <v>32</v>
+      </c>
+      <c r="G707" t="s">
+        <v>32</v>
+      </c>
+      <c r="H707" t="s">
+        <v>32</v>
+      </c>
+      <c r="I707" t="s">
+        <v>32</v>
+      </c>
+      <c r="J707">
+        <v>0</v>
+      </c>
+      <c r="K707" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L707" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M707" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N707" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O707" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P707" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A708" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B708">
+        <v>27</v>
+      </c>
+      <c r="C708">
+        <v>40</v>
+      </c>
+      <c r="D708">
+        <v>1</v>
+      </c>
+      <c r="E708" t="s">
+        <v>32</v>
+      </c>
+      <c r="F708" t="s">
+        <v>32</v>
+      </c>
+      <c r="G708" t="s">
+        <v>32</v>
+      </c>
+      <c r="H708" t="s">
+        <v>32</v>
+      </c>
+      <c r="I708" t="s">
+        <v>32</v>
+      </c>
+      <c r="J708">
+        <v>7</v>
+      </c>
+      <c r="K708" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="L708" s="8">
+        <v>6</v>
+      </c>
+      <c r="M708" s="8">
+        <v>11</v>
+      </c>
+      <c r="N708" s="8">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="O708" s="8">
+        <v>7.9</v>
+      </c>
+      <c r="P708" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A709" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B709">
+        <v>28</v>
+      </c>
+      <c r="C709">
+        <v>40</v>
+      </c>
+      <c r="D709">
+        <v>1</v>
+      </c>
+      <c r="E709" t="s">
+        <v>32</v>
+      </c>
+      <c r="F709" t="s">
+        <v>32</v>
+      </c>
+      <c r="G709" t="s">
+        <v>32</v>
+      </c>
+      <c r="H709" t="s">
+        <v>32</v>
+      </c>
+      <c r="I709" t="s">
+        <v>32</v>
+      </c>
+      <c r="J709">
+        <v>0</v>
+      </c>
+      <c r="K709" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L709" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M709" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N709" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O709" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P709" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A710" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B710">
+        <v>29</v>
+      </c>
+      <c r="C710">
+        <v>40</v>
+      </c>
+      <c r="D710">
+        <v>0</v>
+      </c>
+      <c r="E710" t="s">
+        <v>32</v>
+      </c>
+      <c r="F710" t="s">
+        <v>32</v>
+      </c>
+      <c r="G710" t="s">
+        <v>32</v>
+      </c>
+      <c r="H710" t="s">
+        <v>32</v>
+      </c>
+      <c r="I710" t="s">
+        <v>32</v>
+      </c>
+      <c r="J710">
+        <v>0</v>
+      </c>
+      <c r="K710" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L710" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M710" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N710" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O710" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P710" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A711" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B711">
+        <v>30</v>
+      </c>
+      <c r="C711">
+        <v>40</v>
+      </c>
+      <c r="D711">
+        <v>0</v>
+      </c>
+      <c r="E711" t="s">
+        <v>32</v>
+      </c>
+      <c r="F711" t="s">
+        <v>32</v>
+      </c>
+      <c r="G711" t="s">
+        <v>32</v>
+      </c>
+      <c r="H711" t="s">
+        <v>32</v>
+      </c>
+      <c r="I711" t="s">
+        <v>32</v>
+      </c>
+      <c r="J711">
+        <v>0</v>
+      </c>
+      <c r="K711" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L711" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M711" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N711" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O711" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P711" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A712" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B712">
+        <v>31</v>
+      </c>
+      <c r="C712">
+        <v>40</v>
+      </c>
+      <c r="D712">
+        <v>0</v>
+      </c>
+      <c r="E712" t="s">
+        <v>5</v>
+      </c>
+      <c r="F712" t="s">
+        <v>32</v>
+      </c>
+      <c r="G712" t="s">
+        <v>32</v>
+      </c>
+      <c r="H712" t="s">
+        <v>32</v>
+      </c>
+      <c r="I712" t="s">
+        <v>32</v>
+      </c>
+      <c r="J712">
+        <v>0</v>
+      </c>
+      <c r="K712" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L712" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M712" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N712" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O712" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P712" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A713" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B713">
+        <v>32</v>
+      </c>
+      <c r="C713">
+        <v>40</v>
+      </c>
+      <c r="D713">
+        <v>0</v>
+      </c>
+      <c r="E713" t="s">
+        <v>32</v>
+      </c>
+      <c r="F713" t="s">
+        <v>32</v>
+      </c>
+      <c r="G713" t="s">
+        <v>32</v>
+      </c>
+      <c r="H713" t="s">
+        <v>32</v>
+      </c>
+      <c r="I713" t="s">
+        <v>32</v>
+      </c>
+      <c r="J713">
+        <v>4</v>
+      </c>
+      <c r="K713" s="8">
+        <v>13.9</v>
+      </c>
+      <c r="L713" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="M713" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="N713" s="8">
+        <v>7.9</v>
+      </c>
+      <c r="O713" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P713" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A714" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B714">
+        <v>33</v>
+      </c>
+      <c r="C714">
+        <v>50</v>
+      </c>
+      <c r="D714">
+        <v>1</v>
+      </c>
+      <c r="E714" t="s">
+        <v>32</v>
+      </c>
+      <c r="F714" t="s">
+        <v>32</v>
+      </c>
+      <c r="G714" t="s">
+        <v>32</v>
+      </c>
+      <c r="H714" t="s">
+        <v>32</v>
+      </c>
+      <c r="I714" t="s">
+        <v>32</v>
+      </c>
+      <c r="J714">
+        <v>3</v>
+      </c>
+      <c r="K714" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="L714" s="8">
+        <v>6.6</v>
+      </c>
+      <c r="M714" s="8">
+        <v>10.4</v>
+      </c>
+      <c r="N714" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O714" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P714" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A715" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B715">
+        <v>34</v>
+      </c>
+      <c r="C715">
+        <v>50</v>
+      </c>
+      <c r="D715">
+        <v>1</v>
+      </c>
+      <c r="E715" t="s">
+        <v>32</v>
+      </c>
+      <c r="F715" t="s">
+        <v>32</v>
+      </c>
+      <c r="G715" t="s">
+        <v>32</v>
+      </c>
+      <c r="H715" t="s">
+        <v>32</v>
+      </c>
+      <c r="I715" t="s">
+        <v>32</v>
+      </c>
+      <c r="J715">
+        <v>0</v>
+      </c>
+      <c r="K715" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L715" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M715" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N715" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O715" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P715" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A716" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B716">
+        <v>35</v>
+      </c>
+      <c r="C716">
+        <v>50</v>
+      </c>
+      <c r="D716">
+        <v>1</v>
+      </c>
+      <c r="E716" t="s">
+        <v>32</v>
+      </c>
+      <c r="F716" t="s">
+        <v>32</v>
+      </c>
+      <c r="G716" t="s">
+        <v>32</v>
+      </c>
+      <c r="H716" t="s">
+        <v>32</v>
+      </c>
+      <c r="I716" t="s">
+        <v>32</v>
+      </c>
+      <c r="J716">
+        <v>5</v>
+      </c>
+      <c r="K716" s="8">
+        <v>10.7</v>
+      </c>
+      <c r="L716" s="8">
+        <v>7.9</v>
+      </c>
+      <c r="M716" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="N716" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="O716" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P716" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="717" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A717" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B717">
+        <v>36</v>
+      </c>
+      <c r="C717">
+        <v>50</v>
+      </c>
+      <c r="D717">
+        <v>1</v>
+      </c>
+      <c r="E717" t="s">
+        <v>32</v>
+      </c>
+      <c r="F717" t="s">
+        <v>32</v>
+      </c>
+      <c r="G717" t="s">
+        <v>32</v>
+      </c>
+      <c r="H717" t="s">
+        <v>32</v>
+      </c>
+      <c r="I717" t="s">
+        <v>32</v>
+      </c>
+      <c r="J717">
+        <v>9</v>
+      </c>
+      <c r="K717" s="8">
+        <v>9.5</v>
+      </c>
+      <c r="L717" s="8">
+        <v>6.4</v>
+      </c>
+      <c r="M717" s="8">
+        <v>11.1</v>
+      </c>
+      <c r="N717" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="O717" s="8">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="P717" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A718" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B718">
+        <v>37</v>
+      </c>
+      <c r="C718">
+        <v>50</v>
+      </c>
+      <c r="D718">
+        <v>0</v>
+      </c>
+      <c r="E718" t="s">
+        <v>32</v>
+      </c>
+      <c r="F718" t="s">
+        <v>32</v>
+      </c>
+      <c r="G718" t="s">
+        <v>32</v>
+      </c>
+      <c r="H718" t="s">
+        <v>32</v>
+      </c>
+      <c r="I718" t="s">
+        <v>32</v>
+      </c>
+      <c r="J718">
+        <v>11</v>
+      </c>
+      <c r="K718" s="8">
+        <v>11.8</v>
+      </c>
+      <c r="L718" s="8">
+        <v>7.7</v>
+      </c>
+      <c r="M718" s="8">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N718" s="8">
+        <v>15.3</v>
+      </c>
+      <c r="O718" s="8">
+        <v>7.9</v>
+      </c>
+      <c r="P718" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="719" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A719" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B719">
+        <v>38</v>
+      </c>
+      <c r="C719">
+        <v>50</v>
+      </c>
+      <c r="D719">
+        <v>0</v>
+      </c>
+      <c r="E719" t="s">
+        <v>32</v>
+      </c>
+      <c r="F719" t="s">
+        <v>32</v>
+      </c>
+      <c r="G719" t="s">
+        <v>32</v>
+      </c>
+      <c r="H719" t="s">
+        <v>32</v>
+      </c>
+      <c r="I719" t="s">
+        <v>32</v>
+      </c>
+      <c r="J719">
+        <v>4</v>
+      </c>
+      <c r="K719" s="8">
+        <v>11.6</v>
+      </c>
+      <c r="L719" s="8">
+        <v>7</v>
+      </c>
+      <c r="M719" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="N719" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O719" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P719" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="720" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A720" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B720">
+        <v>39</v>
+      </c>
+      <c r="C720">
+        <v>50</v>
+      </c>
+      <c r="D720">
+        <v>0</v>
+      </c>
+      <c r="E720" t="s">
+        <v>32</v>
+      </c>
+      <c r="F720" t="s">
+        <v>32</v>
+      </c>
+      <c r="G720" t="s">
+        <v>32</v>
+      </c>
+      <c r="H720" t="s">
+        <v>32</v>
+      </c>
+      <c r="I720" t="s">
+        <v>32</v>
+      </c>
+      <c r="J720">
+        <v>0</v>
+      </c>
+      <c r="K720" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L720" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M720" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N720" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O720" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P720" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A721" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B721">
+        <v>40</v>
+      </c>
+      <c r="C721">
+        <v>50</v>
+      </c>
+      <c r="D721">
+        <v>0</v>
+      </c>
+      <c r="E721" t="s">
+        <v>32</v>
+      </c>
+      <c r="F721" t="s">
+        <v>32</v>
+      </c>
+      <c r="G721" t="s">
+        <v>32</v>
+      </c>
+      <c r="H721" t="s">
+        <v>32</v>
+      </c>
+      <c r="I721" t="s">
+        <v>32</v>
+      </c>
+      <c r="J721">
+        <v>4</v>
+      </c>
+      <c r="K721" s="8">
+        <v>13</v>
+      </c>
+      <c r="L721" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="M721" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N721" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O721" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P721" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="722" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A722" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B722">
+        <v>41</v>
+      </c>
+      <c r="C722">
+        <v>60</v>
+      </c>
+      <c r="D722">
+        <v>1</v>
+      </c>
+      <c r="E722" t="s">
+        <v>32</v>
+      </c>
+      <c r="F722" t="s">
+        <v>32</v>
+      </c>
+      <c r="G722" t="s">
+        <v>32</v>
+      </c>
+      <c r="H722" t="s">
+        <v>32</v>
+      </c>
+      <c r="I722" t="s">
+        <v>32</v>
+      </c>
+      <c r="J722">
+        <v>10</v>
+      </c>
+      <c r="K722" s="8">
+        <v>13</v>
+      </c>
+      <c r="L722" s="8">
+        <v>13.9</v>
+      </c>
+      <c r="M722" s="8">
+        <v>9.6</v>
+      </c>
+      <c r="N722" s="8">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="O722" s="8">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="P722" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="723" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A723" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B723">
+        <v>42</v>
+      </c>
+      <c r="C723">
+        <v>60</v>
+      </c>
+      <c r="D723">
+        <v>1</v>
+      </c>
+      <c r="E723" t="s">
+        <v>32</v>
+      </c>
+      <c r="F723" t="s">
+        <v>32</v>
+      </c>
+      <c r="G723" t="s">
+        <v>32</v>
+      </c>
+      <c r="H723" t="s">
+        <v>32</v>
+      </c>
+      <c r="I723" t="s">
+        <v>32</v>
+      </c>
+      <c r="J723">
+        <v>0</v>
+      </c>
+      <c r="K723" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L723" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M723" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N723" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O723" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P723" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="724" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A724" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B724">
+        <v>43</v>
+      </c>
+      <c r="C724">
+        <v>60</v>
+      </c>
+      <c r="D724">
+        <v>1</v>
+      </c>
+      <c r="E724" t="s">
+        <v>32</v>
+      </c>
+      <c r="F724" t="s">
+        <v>32</v>
+      </c>
+      <c r="G724" t="s">
+        <v>32</v>
+      </c>
+      <c r="H724" t="s">
+        <v>32</v>
+      </c>
+      <c r="I724" t="s">
+        <v>32</v>
+      </c>
+      <c r="J724">
+        <v>12</v>
+      </c>
+      <c r="K724" s="8">
+        <v>13.4</v>
+      </c>
+      <c r="L724" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="M724" s="8">
+        <v>8.6</v>
+      </c>
+      <c r="N724" s="8">
+        <v>13.5</v>
+      </c>
+      <c r="O724" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="P724" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="725" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A725" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B725">
+        <v>44</v>
+      </c>
+      <c r="C725">
+        <v>60</v>
+      </c>
+      <c r="D725">
+        <v>1</v>
+      </c>
+      <c r="E725" t="s">
+        <v>32</v>
+      </c>
+      <c r="F725" t="s">
+        <v>32</v>
+      </c>
+      <c r="G725" t="s">
+        <v>32</v>
+      </c>
+      <c r="H725" t="s">
+        <v>32</v>
+      </c>
+      <c r="I725" t="s">
+        <v>32</v>
+      </c>
+      <c r="J725">
+        <v>6</v>
+      </c>
+      <c r="K725" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="L725" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="M725" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="N725" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O725" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P725" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="726" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A726" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B726">
+        <v>45</v>
+      </c>
+      <c r="C726">
+        <v>60</v>
+      </c>
+      <c r="D726">
+        <v>0</v>
+      </c>
+      <c r="E726" t="s">
+        <v>32</v>
+      </c>
+      <c r="F726" t="s">
+        <v>32</v>
+      </c>
+      <c r="G726" t="s">
+        <v>32</v>
+      </c>
+      <c r="H726" t="s">
+        <v>32</v>
+      </c>
+      <c r="I726" t="s">
+        <v>32</v>
+      </c>
+      <c r="J726">
+        <v>13</v>
+      </c>
+      <c r="K726" s="8">
+        <v>13.9</v>
+      </c>
+      <c r="L726" s="8">
+        <v>13.2</v>
+      </c>
+      <c r="M726" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="N726" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="O726" s="8">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="P726" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="727" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A727" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B727">
+        <v>46</v>
+      </c>
+      <c r="C727">
+        <v>60</v>
+      </c>
+      <c r="D727">
+        <v>0</v>
+      </c>
+      <c r="E727" t="s">
+        <v>32</v>
+      </c>
+      <c r="F727" t="s">
+        <v>32</v>
+      </c>
+      <c r="G727" t="s">
+        <v>32</v>
+      </c>
+      <c r="H727" t="s">
+        <v>32</v>
+      </c>
+      <c r="I727" t="s">
+        <v>32</v>
+      </c>
+      <c r="J727">
+        <v>0</v>
+      </c>
+      <c r="K727" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L727" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M727" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N727" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O727" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P727" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="728" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A728" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B728">
+        <v>47</v>
+      </c>
+      <c r="C728">
+        <v>60</v>
+      </c>
+      <c r="D728">
+        <v>0</v>
+      </c>
+      <c r="E728" t="s">
+        <v>32</v>
+      </c>
+      <c r="F728" t="s">
+        <v>32</v>
+      </c>
+      <c r="G728" t="s">
+        <v>32</v>
+      </c>
+      <c r="H728" t="s">
+        <v>32</v>
+      </c>
+      <c r="I728" t="s">
+        <v>32</v>
+      </c>
+      <c r="J728">
+        <v>0</v>
+      </c>
+      <c r="K728" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L728" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M728" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N728" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O728" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P728" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A729" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B729">
+        <v>48</v>
+      </c>
+      <c r="C729">
+        <v>60</v>
+      </c>
+      <c r="D729">
+        <v>0</v>
+      </c>
+      <c r="E729" t="s">
+        <v>32</v>
+      </c>
+      <c r="F729" t="s">
+        <v>32</v>
+      </c>
+      <c r="G729" t="s">
+        <v>32</v>
+      </c>
+      <c r="H729" t="s">
+        <v>32</v>
+      </c>
+      <c r="I729" t="s">
+        <v>32</v>
+      </c>
+      <c r="J729">
+        <v>6</v>
+      </c>
+      <c r="K729" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="L729" s="8">
+        <v>12.4</v>
+      </c>
+      <c r="M729" s="8">
+        <v>9</v>
+      </c>
+      <c r="N729" s="8">
+        <v>2</v>
+      </c>
+      <c r="O729" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P729" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="730" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A730" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B730">
+        <v>49</v>
+      </c>
+      <c r="C730">
+        <v>70</v>
+      </c>
+      <c r="D730">
+        <v>1</v>
+      </c>
+      <c r="E730" t="s">
+        <v>32</v>
+      </c>
+      <c r="F730" t="s">
+        <v>32</v>
+      </c>
+      <c r="G730" t="s">
+        <v>32</v>
+      </c>
+      <c r="H730" t="s">
+        <v>32</v>
+      </c>
+      <c r="I730" t="s">
+        <v>32</v>
+      </c>
+      <c r="J730">
+        <v>25</v>
+      </c>
+      <c r="K730" s="8">
+        <v>12.4</v>
+      </c>
+      <c r="L730" s="8">
+        <v>11.5</v>
+      </c>
+      <c r="M730" s="8">
+        <v>10</v>
+      </c>
+      <c r="N730" s="8">
+        <v>12.3</v>
+      </c>
+      <c r="O730" s="8">
+        <v>9.4</v>
+      </c>
+      <c r="P730" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="731" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A731" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B731">
+        <v>50</v>
+      </c>
+      <c r="C731">
+        <v>70</v>
+      </c>
+      <c r="D731">
+        <v>1</v>
+      </c>
+      <c r="E731" t="s">
+        <v>32</v>
+      </c>
+      <c r="F731" t="s">
+        <v>32</v>
+      </c>
+      <c r="G731" t="s">
+        <v>32</v>
+      </c>
+      <c r="H731" t="s">
+        <v>32</v>
+      </c>
+      <c r="I731" t="s">
+        <v>32</v>
+      </c>
+      <c r="J731">
+        <v>0</v>
+      </c>
+      <c r="K731" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L731" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M731" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N731" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O731" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P731" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="732" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A732" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B732">
+        <v>51</v>
+      </c>
+      <c r="C732">
+        <v>70</v>
+      </c>
+      <c r="D732">
+        <v>1</v>
+      </c>
+      <c r="E732" t="s">
+        <v>32</v>
+      </c>
+      <c r="F732" t="s">
+        <v>32</v>
+      </c>
+      <c r="G732" t="s">
+        <v>32</v>
+      </c>
+      <c r="H732" t="s">
+        <v>32</v>
+      </c>
+      <c r="I732" t="s">
+        <v>32</v>
+      </c>
+      <c r="J732">
+        <v>0</v>
+      </c>
+      <c r="K732" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L732" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M732" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N732" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O732" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P732" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A733" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B733">
+        <v>52</v>
+      </c>
+      <c r="C733">
+        <v>70</v>
+      </c>
+      <c r="D733">
+        <v>1</v>
+      </c>
+      <c r="E733" t="s">
+        <v>32</v>
+      </c>
+      <c r="F733" t="s">
+        <v>32</v>
+      </c>
+      <c r="G733" t="s">
+        <v>32</v>
+      </c>
+      <c r="H733" t="s">
+        <v>32</v>
+      </c>
+      <c r="I733" t="s">
+        <v>32</v>
+      </c>
+      <c r="J733">
+        <v>0</v>
+      </c>
+      <c r="K733" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L733" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M733" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N733" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O733" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P733" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="734" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A734" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B734">
+        <v>53</v>
+      </c>
+      <c r="C734">
+        <v>70</v>
+      </c>
+      <c r="D734">
+        <v>0</v>
+      </c>
+      <c r="E734" t="s">
+        <v>32</v>
+      </c>
+      <c r="F734" t="s">
+        <v>32</v>
+      </c>
+      <c r="G734" t="s">
+        <v>32</v>
+      </c>
+      <c r="H734" t="s">
+        <v>32</v>
+      </c>
+      <c r="I734" t="s">
+        <v>32</v>
+      </c>
+      <c r="J734">
+        <v>0</v>
+      </c>
+      <c r="K734" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L734" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M734" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N734" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O734" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P734" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="735" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A735" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B735">
+        <v>54</v>
+      </c>
+      <c r="C735">
+        <v>70</v>
+      </c>
+      <c r="D735">
+        <v>0</v>
+      </c>
+      <c r="E735" t="s">
+        <v>32</v>
+      </c>
+      <c r="F735" t="s">
+        <v>32</v>
+      </c>
+      <c r="G735" t="s">
+        <v>32</v>
+      </c>
+      <c r="H735" t="s">
+        <v>32</v>
+      </c>
+      <c r="I735" t="s">
+        <v>32</v>
+      </c>
+      <c r="J735">
+        <v>12</v>
+      </c>
+      <c r="K735" s="8">
+        <v>14.1</v>
+      </c>
+      <c r="L735" s="8">
+        <v>9.5</v>
+      </c>
+      <c r="M735" s="8">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="N735" s="8">
+        <v>9.4</v>
+      </c>
+      <c r="O735" s="8">
+        <v>7.6</v>
+      </c>
+      <c r="P735" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="736" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A736" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B736">
+        <v>55</v>
+      </c>
+      <c r="C736">
+        <v>70</v>
+      </c>
+      <c r="D736">
+        <v>0</v>
+      </c>
+      <c r="E736" t="s">
+        <v>32</v>
+      </c>
+      <c r="F736" t="s">
+        <v>32</v>
+      </c>
+      <c r="G736" t="s">
+        <v>32</v>
+      </c>
+      <c r="H736" t="s">
+        <v>32</v>
+      </c>
+      <c r="I736" t="s">
+        <v>32</v>
+      </c>
+      <c r="J736">
+        <v>18</v>
+      </c>
+      <c r="K736" s="8">
+        <v>9.5</v>
+      </c>
+      <c r="L736" s="8">
+        <v>11.2</v>
+      </c>
+      <c r="M736" s="8">
+        <v>12.7</v>
+      </c>
+      <c r="N736" s="8">
+        <v>12.8</v>
+      </c>
+      <c r="O736" s="8">
+        <v>9.6</v>
+      </c>
+      <c r="P736" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="737" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A737" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B737">
+        <v>56</v>
+      </c>
+      <c r="C737">
+        <v>70</v>
+      </c>
+      <c r="D737">
+        <v>0</v>
+      </c>
+      <c r="E737" t="s">
+        <v>32</v>
+      </c>
+      <c r="F737" t="s">
+        <v>32</v>
+      </c>
+      <c r="G737" t="s">
+        <v>32</v>
+      </c>
+      <c r="H737" t="s">
+        <v>32</v>
+      </c>
+      <c r="I737" t="s">
+        <v>32</v>
+      </c>
+      <c r="J737">
+        <v>4</v>
+      </c>
+      <c r="K737" s="8">
+        <v>12.9</v>
+      </c>
+      <c r="L737" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="M737" s="8">
+        <v>15</v>
+      </c>
+      <c r="N737" s="8">
+        <v>13.9</v>
+      </c>
+      <c r="O737" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P737" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A738" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B738">
+        <v>57</v>
+      </c>
+      <c r="C738">
+        <v>80</v>
+      </c>
+      <c r="D738">
+        <v>1</v>
+      </c>
+      <c r="E738" t="s">
+        <v>32</v>
+      </c>
+      <c r="F738" t="s">
+        <v>32</v>
+      </c>
+      <c r="G738" t="s">
+        <v>32</v>
+      </c>
+      <c r="H738" t="s">
+        <v>32</v>
+      </c>
+      <c r="I738" t="s">
+        <v>32</v>
+      </c>
+      <c r="J738">
+        <v>0</v>
+      </c>
+      <c r="K738" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L738" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M738" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N738" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O738" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P738" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="739" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A739" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B739">
+        <v>58</v>
+      </c>
+      <c r="C739">
+        <v>80</v>
+      </c>
+      <c r="D739">
+        <v>1</v>
+      </c>
+      <c r="E739" t="s">
+        <v>32</v>
+      </c>
+      <c r="F739" t="s">
+        <v>32</v>
+      </c>
+      <c r="G739" t="s">
+        <v>32</v>
+      </c>
+      <c r="H739" t="s">
+        <v>32</v>
+      </c>
+      <c r="I739" t="s">
+        <v>32</v>
+      </c>
+      <c r="J739">
+        <v>0</v>
+      </c>
+      <c r="K739" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L739" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M739" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N739" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O739" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P739" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="740" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A740" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B740">
+        <v>59</v>
+      </c>
+      <c r="C740">
+        <v>80</v>
+      </c>
+      <c r="D740">
+        <v>1</v>
+      </c>
+      <c r="E740" t="s">
+        <v>32</v>
+      </c>
+      <c r="F740" t="s">
+        <v>32</v>
+      </c>
+      <c r="G740" t="s">
+        <v>32</v>
+      </c>
+      <c r="H740" t="s">
+        <v>32</v>
+      </c>
+      <c r="I740" t="s">
+        <v>32</v>
+      </c>
+      <c r="J740">
+        <v>23</v>
+      </c>
+      <c r="K740" s="8">
+        <v>10.6</v>
+      </c>
+      <c r="L740" s="8">
+        <v>12.9</v>
+      </c>
+      <c r="M740" s="8">
+        <v>10.4</v>
+      </c>
+      <c r="N740" s="8">
+        <v>12.8</v>
+      </c>
+      <c r="O740" s="8">
+        <v>14.7</v>
+      </c>
+      <c r="P740" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="741" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A741" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B741">
+        <v>60</v>
+      </c>
+      <c r="C741">
+        <v>80</v>
+      </c>
+      <c r="D741">
+        <v>1</v>
+      </c>
+      <c r="E741" t="s">
+        <v>32</v>
+      </c>
+      <c r="F741" t="s">
+        <v>32</v>
+      </c>
+      <c r="G741" t="s">
+        <v>32</v>
+      </c>
+      <c r="H741" t="s">
+        <v>32</v>
+      </c>
+      <c r="I741" t="s">
+        <v>32</v>
+      </c>
+      <c r="J741">
+        <v>6</v>
+      </c>
+      <c r="K741" s="8">
+        <v>12.7</v>
+      </c>
+      <c r="L741" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="M741" s="8">
+        <v>7.4</v>
+      </c>
+      <c r="N741" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O741" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P741" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="742" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A742" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B742">
+        <v>61</v>
+      </c>
+      <c r="C742">
+        <v>80</v>
+      </c>
+      <c r="D742">
+        <v>0</v>
+      </c>
+      <c r="E742" t="s">
+        <v>32</v>
+      </c>
+      <c r="F742" t="s">
+        <v>32</v>
+      </c>
+      <c r="G742" t="s">
+        <v>32</v>
+      </c>
+      <c r="H742" t="s">
+        <v>32</v>
+      </c>
+      <c r="I742" t="s">
+        <v>32</v>
+      </c>
+      <c r="J742">
+        <v>4</v>
+      </c>
+      <c r="K742" s="8">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="L742" s="8">
+        <v>12.1</v>
+      </c>
+      <c r="M742" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="N742" s="8">
+        <v>11.4</v>
+      </c>
+      <c r="O742" s="8">
+        <v>11.1</v>
+      </c>
+      <c r="P742" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="743" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A743" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B743">
+        <v>62</v>
+      </c>
+      <c r="C743">
+        <v>80</v>
+      </c>
+      <c r="D743">
+        <v>0</v>
+      </c>
+      <c r="E743" t="s">
+        <v>32</v>
+      </c>
+      <c r="F743" t="s">
+        <v>32</v>
+      </c>
+      <c r="G743" t="s">
+        <v>32</v>
+      </c>
+      <c r="H743" t="s">
+        <v>32</v>
+      </c>
+      <c r="I743" t="s">
+        <v>32</v>
+      </c>
+      <c r="J743">
+        <v>0</v>
+      </c>
+      <c r="K743" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L743" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M743" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N743" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O743" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P743" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="744" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A744" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B744">
+        <v>63</v>
+      </c>
+      <c r="C744">
+        <v>80</v>
+      </c>
+      <c r="D744">
+        <v>0</v>
+      </c>
+      <c r="E744" t="s">
+        <v>32</v>
+      </c>
+      <c r="F744" t="s">
+        <v>32</v>
+      </c>
+      <c r="G744" t="s">
+        <v>32</v>
+      </c>
+      <c r="H744" t="s">
+        <v>32</v>
+      </c>
+      <c r="I744" t="s">
+        <v>32</v>
+      </c>
+      <c r="J744">
+        <v>0</v>
+      </c>
+      <c r="K744" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L744" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M744" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N744" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O744" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P744" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="745" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A745" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B745">
+        <v>64</v>
+      </c>
+      <c r="C745">
+        <v>80</v>
+      </c>
+      <c r="D745">
+        <v>0</v>
+      </c>
+      <c r="E745" t="s">
+        <v>32</v>
+      </c>
+      <c r="F745" t="s">
+        <v>32</v>
+      </c>
+      <c r="G745" t="s">
+        <v>32</v>
+      </c>
+      <c r="H745" t="s">
+        <v>32</v>
+      </c>
+      <c r="I745" t="s">
+        <v>32</v>
+      </c>
+      <c r="J745">
+        <v>6</v>
+      </c>
+      <c r="K745" s="8">
+        <v>12.7</v>
+      </c>
+      <c r="L745" s="8">
+        <v>11.8</v>
+      </c>
+      <c r="M745" s="8">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="N745" s="8">
+        <v>12.4</v>
+      </c>
+      <c r="O745" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="P745" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="746" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A746" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B746">
+        <v>65</v>
+      </c>
+      <c r="C746">
+        <v>90</v>
+      </c>
+      <c r="D746">
+        <v>1</v>
+      </c>
+      <c r="E746" t="s">
+        <v>32</v>
+      </c>
+      <c r="F746" t="s">
+        <v>32</v>
+      </c>
+      <c r="G746" t="s">
+        <v>32</v>
+      </c>
+      <c r="H746" t="s">
+        <v>32</v>
+      </c>
+      <c r="I746" t="s">
+        <v>32</v>
+      </c>
+      <c r="J746">
+        <v>11</v>
+      </c>
+      <c r="K746" s="8">
+        <v>7</v>
+      </c>
+      <c r="L746" s="8">
+        <v>12.1</v>
+      </c>
+      <c r="M746" s="8">
+        <v>7.7</v>
+      </c>
+      <c r="N746" s="8">
+        <v>12.6</v>
+      </c>
+      <c r="O746" s="8">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="P746" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="747" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A747" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B747">
+        <v>66</v>
+      </c>
+      <c r="C747">
+        <v>90</v>
+      </c>
+      <c r="D747">
+        <v>1</v>
+      </c>
+      <c r="E747" t="s">
+        <v>32</v>
+      </c>
+      <c r="F747" t="s">
+        <v>32</v>
+      </c>
+      <c r="G747" t="s">
+        <v>32</v>
+      </c>
+      <c r="H747" t="s">
+        <v>32</v>
+      </c>
+      <c r="I747" t="s">
+        <v>32</v>
+      </c>
+      <c r="J747">
+        <v>0</v>
+      </c>
+      <c r="K747" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L747" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M747" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N747" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O747" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P747" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="748" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A748" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B748">
+        <v>67</v>
+      </c>
+      <c r="C748">
+        <v>90</v>
+      </c>
+      <c r="D748">
+        <v>1</v>
+      </c>
+      <c r="E748" t="s">
+        <v>32</v>
+      </c>
+      <c r="F748" t="s">
+        <v>32</v>
+      </c>
+      <c r="G748" t="s">
+        <v>32</v>
+      </c>
+      <c r="H748" t="s">
+        <v>32</v>
+      </c>
+      <c r="I748" t="s">
+        <v>32</v>
+      </c>
+      <c r="J748">
+        <v>0</v>
+      </c>
+      <c r="K748" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L748" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M748" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N748" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O748" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P748" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="749" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A749" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B749">
+        <v>68</v>
+      </c>
+      <c r="C749">
+        <v>90</v>
+      </c>
+      <c r="D749">
+        <v>1</v>
+      </c>
+      <c r="E749" t="s">
+        <v>32</v>
+      </c>
+      <c r="F749" t="s">
+        <v>32</v>
+      </c>
+      <c r="G749" t="s">
+        <v>32</v>
+      </c>
+      <c r="H749" t="s">
+        <v>32</v>
+      </c>
+      <c r="I749" t="s">
+        <v>32</v>
+      </c>
+      <c r="J749">
+        <v>14</v>
+      </c>
+      <c r="K749" s="8">
+        <v>9</v>
+      </c>
+      <c r="L749" s="8">
+        <v>5.8</v>
+      </c>
+      <c r="M749" s="8">
+        <v>9</v>
+      </c>
+      <c r="N749" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O749" s="8">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="P749" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="750" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A750" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B750">
+        <v>69</v>
+      </c>
+      <c r="C750">
+        <v>90</v>
+      </c>
+      <c r="D750">
+        <v>0</v>
+      </c>
+      <c r="E750" t="s">
+        <v>32</v>
+      </c>
+      <c r="F750" t="s">
+        <v>32</v>
+      </c>
+      <c r="G750" t="s">
+        <v>32</v>
+      </c>
+      <c r="H750" t="s">
+        <v>32</v>
+      </c>
+      <c r="I750" t="s">
+        <v>32</v>
+      </c>
+      <c r="J750">
+        <v>27</v>
+      </c>
+      <c r="K750" s="8">
+        <v>6</v>
+      </c>
+      <c r="L750" s="8">
+        <v>13.2</v>
+      </c>
+      <c r="M750" s="8">
+        <v>10.1</v>
+      </c>
+      <c r="N750" s="8">
+        <v>11.5</v>
+      </c>
+      <c r="O750" s="8">
+        <v>8.6</v>
+      </c>
+      <c r="P750" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="751" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A751" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B751">
+        <v>70</v>
+      </c>
+      <c r="C751">
+        <v>90</v>
+      </c>
+      <c r="D751">
+        <v>0</v>
+      </c>
+      <c r="E751" t="s">
+        <v>32</v>
+      </c>
+      <c r="F751" t="s">
+        <v>32</v>
+      </c>
+      <c r="G751" t="s">
+        <v>32</v>
+      </c>
+      <c r="H751" t="s">
+        <v>32</v>
+      </c>
+      <c r="I751" t="s">
+        <v>32</v>
+      </c>
+      <c r="J751">
+        <v>4</v>
+      </c>
+      <c r="K751" s="8">
+        <v>13.9</v>
+      </c>
+      <c r="L751" s="8">
+        <v>8</v>
+      </c>
+      <c r="M751" s="8">
+        <v>11.5</v>
+      </c>
+      <c r="N751" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O751" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P751" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="752" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A752" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B752">
+        <v>71</v>
+      </c>
+      <c r="C752">
+        <v>90</v>
+      </c>
+      <c r="D752">
+        <v>0</v>
+      </c>
+      <c r="E752" t="s">
+        <v>32</v>
+      </c>
+      <c r="F752" t="s">
+        <v>32</v>
+      </c>
+      <c r="G752" t="s">
+        <v>32</v>
+      </c>
+      <c r="H752" t="s">
+        <v>32</v>
+      </c>
+      <c r="I752" t="s">
+        <v>32</v>
+      </c>
+      <c r="J752">
+        <v>0</v>
+      </c>
+      <c r="K752" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L752" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M752" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N752" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O752" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P752" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="753" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A753" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B753">
+        <v>72</v>
+      </c>
+      <c r="C753">
+        <v>90</v>
+      </c>
+      <c r="D753">
+        <v>0</v>
+      </c>
+      <c r="E753" t="s">
+        <v>32</v>
+      </c>
+      <c r="F753" t="s">
+        <v>32</v>
+      </c>
+      <c r="G753" t="s">
+        <v>32</v>
+      </c>
+      <c r="H753" t="s">
+        <v>32</v>
+      </c>
+      <c r="I753" t="s">
+        <v>32</v>
+      </c>
+      <c r="J753">
+        <v>3</v>
+      </c>
+      <c r="K753" s="8">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="L753" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="M753" s="8">
+        <v>7.8</v>
+      </c>
+      <c r="N753" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O753" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P753" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="754" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A754" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B754">
+        <v>73</v>
+      </c>
+      <c r="C754">
+        <v>100</v>
+      </c>
+      <c r="D754">
+        <v>1</v>
+      </c>
+      <c r="E754" t="s">
+        <v>32</v>
+      </c>
+      <c r="F754" t="s">
+        <v>32</v>
+      </c>
+      <c r="G754" t="s">
+        <v>32</v>
+      </c>
+      <c r="H754" t="s">
+        <v>32</v>
+      </c>
+      <c r="I754" t="s">
+        <v>32</v>
+      </c>
+      <c r="J754">
+        <v>6</v>
+      </c>
+      <c r="K754" s="8">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L754" s="8">
+        <v>11.1</v>
+      </c>
+      <c r="M754" s="8">
+        <v>11.2</v>
+      </c>
+      <c r="N754" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O754" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P754" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="755" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A755" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B755">
+        <v>74</v>
+      </c>
+      <c r="C755">
+        <v>100</v>
+      </c>
+      <c r="D755">
+        <v>1</v>
+      </c>
+      <c r="E755" t="s">
+        <v>32</v>
+      </c>
+      <c r="F755" t="s">
+        <v>32</v>
+      </c>
+      <c r="G755" t="s">
+        <v>32</v>
+      </c>
+      <c r="H755" t="s">
+        <v>32</v>
+      </c>
+      <c r="I755" t="s">
+        <v>32</v>
+      </c>
+      <c r="J755">
+        <v>12</v>
+      </c>
+      <c r="K755" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="L755" s="8">
+        <v>10.4</v>
+      </c>
+      <c r="M755" s="8">
+        <v>14</v>
+      </c>
+      <c r="N755" s="8">
+        <v>12.8</v>
+      </c>
+      <c r="O755" s="8">
+        <v>12.2</v>
+      </c>
+      <c r="P755" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="756" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A756" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B756">
+        <v>75</v>
+      </c>
+      <c r="C756">
+        <v>100</v>
+      </c>
+      <c r="D756">
+        <v>1</v>
+      </c>
+      <c r="E756" t="s">
+        <v>32</v>
+      </c>
+      <c r="F756" t="s">
+        <v>32</v>
+      </c>
+      <c r="G756" t="s">
+        <v>32</v>
+      </c>
+      <c r="H756" t="s">
+        <v>32</v>
+      </c>
+      <c r="I756" t="s">
+        <v>32</v>
+      </c>
+      <c r="J756">
+        <v>7</v>
+      </c>
+      <c r="K756" s="8">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L756" s="8">
+        <v>15.2</v>
+      </c>
+      <c r="M756" s="8">
+        <v>11.1</v>
+      </c>
+      <c r="N756" s="8">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="O756" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="P756" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="757" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A757" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B757">
+        <v>76</v>
+      </c>
+      <c r="C757">
+        <v>100</v>
+      </c>
+      <c r="D757">
+        <v>1</v>
+      </c>
+      <c r="E757" t="s">
+        <v>32</v>
+      </c>
+      <c r="F757" t="s">
+        <v>32</v>
+      </c>
+      <c r="G757" t="s">
+        <v>32</v>
+      </c>
+      <c r="H757" t="s">
+        <v>32</v>
+      </c>
+      <c r="I757" t="s">
+        <v>32</v>
+      </c>
+      <c r="J757">
+        <v>0</v>
+      </c>
+      <c r="K757" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L757" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M757" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N757" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O757" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P757" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="758" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A758" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B758">
+        <v>77</v>
+      </c>
+      <c r="C758">
+        <v>100</v>
+      </c>
+      <c r="D758">
+        <v>0</v>
+      </c>
+      <c r="E758" t="s">
+        <v>32</v>
+      </c>
+      <c r="F758" t="s">
+        <v>32</v>
+      </c>
+      <c r="G758" t="s">
+        <v>32</v>
+      </c>
+      <c r="H758" t="s">
+        <v>32</v>
+      </c>
+      <c r="I758" t="s">
+        <v>32</v>
+      </c>
+      <c r="J758">
+        <v>12</v>
+      </c>
+      <c r="K758" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="L758" s="8">
+        <v>12.5</v>
+      </c>
+      <c r="M758" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N758" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O758" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P758" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="759" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A759" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B759">
+        <v>78</v>
+      </c>
+      <c r="C759">
+        <v>100</v>
+      </c>
+      <c r="D759">
+        <v>0</v>
+      </c>
+      <c r="E759" t="s">
+        <v>32</v>
+      </c>
+      <c r="F759" t="s">
+        <v>32</v>
+      </c>
+      <c r="G759" t="s">
+        <v>32</v>
+      </c>
+      <c r="H759" t="s">
+        <v>32</v>
+      </c>
+      <c r="I759" t="s">
+        <v>32</v>
+      </c>
+      <c r="J759">
+        <v>10</v>
+      </c>
+      <c r="K759" s="8">
+        <v>13.1</v>
+      </c>
+      <c r="L759" s="8">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="M759" s="8">
+        <v>9.4</v>
+      </c>
+      <c r="N759" s="8">
+        <v>18.7</v>
+      </c>
+      <c r="O759" s="8">
+        <v>18</v>
+      </c>
+      <c r="P759" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="760" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A760" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B760">
+        <v>79</v>
+      </c>
+      <c r="C760">
+        <v>100</v>
+      </c>
+      <c r="D760">
+        <v>0</v>
+      </c>
+      <c r="E760" t="s">
+        <v>32</v>
+      </c>
+      <c r="F760" t="s">
+        <v>32</v>
+      </c>
+      <c r="G760" t="s">
+        <v>32</v>
+      </c>
+      <c r="H760" t="s">
+        <v>32</v>
+      </c>
+      <c r="I760" t="s">
+        <v>32</v>
+      </c>
+      <c r="J760">
+        <v>5</v>
+      </c>
+      <c r="K760" s="8">
+        <v>10.6</v>
+      </c>
+      <c r="L760" s="8">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="M760" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N760" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O760" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P760" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="761" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A761" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B761">
+        <v>80</v>
+      </c>
+      <c r="C761">
+        <v>100</v>
+      </c>
+      <c r="D761">
+        <v>0</v>
+      </c>
+      <c r="E761" t="s">
+        <v>32</v>
+      </c>
+      <c r="F761" t="s">
+        <v>32</v>
+      </c>
+      <c r="G761" t="s">
+        <v>32</v>
+      </c>
+      <c r="H761" t="s">
+        <v>32</v>
+      </c>
+      <c r="I761" t="s">
+        <v>32</v>
+      </c>
+      <c r="J761">
+        <v>6</v>
+      </c>
+      <c r="K761" s="8">
+        <v>7.4</v>
+      </c>
+      <c r="L761" s="8">
+        <v>13.6</v>
+      </c>
+      <c r="M761" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N761" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O761" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P761" s="8">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -35954,15 +39960,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="bf323757-61cd-4801-a443-23c940188ab5" xsi:nil="true"/>
@@ -35971,6 +39968,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -36181,14 +40187,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDD08229-D6B3-4C31-8075-C61C74A3E90D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D85CC4B6-E7C5-4B39-9FAE-D8B1E7E52F68}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="ca0917e0-7ee0-43e8-b41f-f2ef8ec07696"/>
@@ -36201,6 +40199,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDD08229-D6B3-4C31-8075-C61C74A3E90D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
